--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEW_YORK_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEW_YORK_2010.xlsx
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C105">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C719">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C916">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C955">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1055">
